--- a/product_selector_out/STM32L4x6 - diff.xlsx
+++ b/product_selector_out/STM32L4x6 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +48,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,13 +81,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +549,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -591,7 +609,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +619,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -611,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2170</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="18">
@@ -787,18 +805,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -810,59 +832,67 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -874,18 +904,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -897,18 +927,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -920,18 +950,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -943,18 +973,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -966,18 +996,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -989,76 +1019,88 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1081,7 +1123,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1104,7 +1146,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1127,7 +1169,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1150,87 +1192,99 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -1242,18 +1296,18 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -1265,76 +1319,88 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1357,7 +1423,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1380,7 +1446,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1403,7 +1469,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1426,7 +1492,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1449,7 +1515,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1472,7 +1538,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1495,7 +1561,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1518,7 +1584,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1541,7 +1607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1564,7 +1630,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1587,7 +1653,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1610,7 +1676,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1633,7 +1699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1656,7 +1722,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1679,7 +1745,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1702,7 +1768,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1725,7 +1791,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1748,7 +1814,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1771,7 +1837,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1794,7 +1860,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1817,7 +1883,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1840,7 +1906,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1863,7 +1929,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1886,7 +1952,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1909,7 +1975,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1932,7 +1998,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1955,7 +2021,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1978,7 +2044,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2001,7 +2067,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2024,7 +2090,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2047,7 +2113,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2070,7 +2136,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2093,7 +2159,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2116,7 +2182,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2139,7 +2205,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2162,7 +2228,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2185,7 +2251,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2208,7 +2274,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2231,7 +2297,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2251,8 +2317,365 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>STM32L476RE</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>STM32L496RG</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>STM32L496ZG</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>STM32L476ME</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A18:E88"/>
+  <autoFilter ref="A18:E103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32L4x6 - diff.xlsx
+++ b/product_selector_out/STM32L4x6 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2240</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="6">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2165</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="18">
@@ -927,18 +927,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L4A6ZG</t>
+          <t>STM32L486ZG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -955,13 +955,13 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -973,18 +973,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L476JG</t>
+          <t>STM32L4A6ZG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1001,13 +1001,13 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
@@ -1019,27 +1019,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L486QG</t>
+          <t>STM32L476JG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1064,9 +1060,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1079,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1091,9 +1087,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1105,18 +1101,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1128,13 +1128,13 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -1146,18 +1146,18 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1169,18 +1169,18 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L496QE</t>
+          <t>STM32L486QG</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -1192,54 +1192,46 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L486JG</t>
+          <t>STM32L496QE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1248,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>9 (workbook and API agree)</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1264,9 +1256,9 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1278,18 +1270,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1301,99 +1297,91 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L486VG</t>
+          <t>STM32L486JG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1405,18 +1393,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1428,59 +1420,67 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L4A6QG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -1492,18 +1492,18 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1515,18 +1515,18 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L4A6VG</t>
+          <t>STM32L486VG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -1538,7 +1538,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1561,7 +1561,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L476VC</t>
+          <t>STM32L4A6QG</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1584,7 +1584,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1607,7 +1607,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L4A6RG</t>
+          <t>STM32L4A6VG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L476QG</t>
+          <t>STM32L476VC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L496VE</t>
+          <t>STM32L4A6RG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1722,7 +1722,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1745,7 +1745,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L476VG</t>
+          <t>STM32L476QG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1791,7 +1791,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L496RE</t>
+          <t>STM32L496VE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1814,7 +1814,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1837,7 +1837,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L476RG</t>
+          <t>STM32L476VG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1860,7 +1860,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1883,7 +1883,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L496AE</t>
+          <t>STM32L496RE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1929,7 +1929,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L496ZE</t>
+          <t>STM32L476RG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1952,7 +1952,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L476ZE</t>
+          <t>STM32L496AE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1998,7 +1998,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L476ZG</t>
+          <t>STM32L496ZE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32L496VG</t>
+          <t>STM32L476ZE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2090,7 +2090,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2113,7 +2113,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32L496QG</t>
+          <t>STM32L476ZG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2136,7 +2136,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32L476MG</t>
+          <t>STM32L496VG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2182,7 +2182,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2205,7 +2205,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32L496AG</t>
+          <t>STM32L496QG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2228,7 +2228,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32L476QE</t>
+          <t>STM32L476MG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2274,7 +2274,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32L476VE</t>
+          <t>STM32L496AG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32L476RE</t>
+          <t>STM32L476QE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2366,7 +2366,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32L496RG</t>
+          <t>STM32L476VE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2412,7 +2412,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2435,7 +2435,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32L496ZG</t>
+          <t>STM32L476RE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2458,7 +2458,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2481,7 +2481,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32L476ME</t>
+          <t>STM32L496RG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2504,99 +2504,87 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496ZG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L496ZG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476ME</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>9 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32L486RG</t>
+          <t>STM32L476ME</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -2613,69 +2601,196 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32L496WG</t>
+          <t>STM32L486RG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>9 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32L486RG</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>STM32L496WG</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32L496WG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E103"/>
+  <autoFilter ref="A18:E108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>